--- a/artfynd/A 25130-2026 artfynd.xlsx
+++ b/artfynd/A 25130-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648232</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25130-2026 artfynd.xlsx
+++ b/artfynd/A 25130-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648232</v>
       </c>
       <c r="B2" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25130-2026 artfynd.xlsx
+++ b/artfynd/A 25130-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648232</v>
       </c>
       <c r="B2" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136648207</v>
       </c>
       <c r="B3" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136648277</v>
       </c>
       <c r="B4" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136648220</v>
       </c>
       <c r="B5" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136648255</v>
       </c>
       <c r="B6" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25130-2026 artfynd.xlsx
+++ b/artfynd/A 25130-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648232</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25130-2026 artfynd.xlsx
+++ b/artfynd/A 25130-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648232</v>
       </c>
       <c r="B2" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136648207</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136648277</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25130-2026 artfynd.xlsx
+++ b/artfynd/A 25130-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648232</v>
       </c>
       <c r="B2" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136648207</v>
       </c>
       <c r="B3" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136648277</v>
       </c>
       <c r="B4" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25130-2026 artfynd.xlsx
+++ b/artfynd/A 25130-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648232</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136648207</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136648277</v>
       </c>
       <c r="B4" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25130-2026 artfynd.xlsx
+++ b/artfynd/A 25130-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648232</v>
       </c>
       <c r="B2" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
